--- a/artfynd/A 5160-2022 artfynd.xlsx
+++ b/artfynd/A 5160-2022 artfynd.xlsx
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117912929</v>
+        <v>117911924</v>
       </c>
       <c r="B6" t="n">
-        <v>58130</v>
+        <v>57287</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,51 +1115,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>208249</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kall NNÖ, Jmt</t>
+          <t>Koberget VNV Kall, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>417672</v>
+        <v>417558</v>
       </c>
       <c r="R6" t="n">
-        <v>7047296</v>
+        <v>7047233</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,13 +1181,17 @@
           <t>2024-06-20</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1219,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117911924</v>
+        <v>117912929</v>
       </c>
       <c r="B7" t="n">
-        <v>57287</v>
+        <v>58130</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1231,38 +1222,51 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>208249</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Koberget VNV Kall, Jmt</t>
+          <t>Kall NNÖ, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>417558</v>
+        <v>417672</v>
       </c>
       <c r="R7" t="n">
-        <v>7047233</v>
+        <v>7047296</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,17 +1301,13 @@
           <t>2024-06-20</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 5160-2022 artfynd.xlsx
+++ b/artfynd/A 5160-2022 artfynd.xlsx
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117911924</v>
+        <v>117912929</v>
       </c>
       <c r="B6" t="n">
-        <v>57287</v>
+        <v>58131</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,38 +1115,51 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>208249</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Koberget VNV Kall, Jmt</t>
+          <t>Kall NNÖ, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>417558</v>
+        <v>417672</v>
       </c>
       <c r="R6" t="n">
-        <v>7047233</v>
+        <v>7047296</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1181,17 +1194,13 @@
           <t>2024-06-20</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1210,10 +1219,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117912929</v>
+        <v>117911926</v>
       </c>
       <c r="B7" t="n">
-        <v>58130</v>
+        <v>57288</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,51 +1231,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>208249</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kall NNÖ, Jmt</t>
+          <t>Koberget VNV Kall, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>417672</v>
+        <v>417584</v>
       </c>
       <c r="R7" t="n">
-        <v>7047296</v>
+        <v>7047126</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1301,13 +1297,17 @@
           <t>2024-06-20</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1326,10 +1326,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117911926</v>
+        <v>117911924</v>
       </c>
       <c r="B8" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1366,10 +1366,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>417584</v>
+        <v>417558</v>
       </c>
       <c r="R8" t="n">
-        <v>7047126</v>
+        <v>7047233</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 5160-2022 artfynd.xlsx
+++ b/artfynd/A 5160-2022 artfynd.xlsx
@@ -1219,7 +1219,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117911924</v>
+        <v>117911926</v>
       </c>
       <c r="B7" t="n">
         <v>57290</v>
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>417558</v>
+        <v>417584</v>
       </c>
       <c r="R7" t="n">
-        <v>7047233</v>
+        <v>7047126</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1326,7 +1326,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117911926</v>
+        <v>117911924</v>
       </c>
       <c r="B8" t="n">
         <v>57290</v>
@@ -1366,10 +1366,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>417584</v>
+        <v>417558</v>
       </c>
       <c r="R8" t="n">
-        <v>7047126</v>
+        <v>7047233</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 5160-2022 artfynd.xlsx
+++ b/artfynd/A 5160-2022 artfynd.xlsx
@@ -1219,7 +1219,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117911926</v>
+        <v>117911924</v>
       </c>
       <c r="B7" t="n">
         <v>57290</v>
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>417584</v>
+        <v>417558</v>
       </c>
       <c r="R7" t="n">
-        <v>7047126</v>
+        <v>7047233</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1326,7 +1326,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117911924</v>
+        <v>117911926</v>
       </c>
       <c r="B8" t="n">
         <v>57290</v>
@@ -1366,10 +1366,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>417558</v>
+        <v>417584</v>
       </c>
       <c r="R8" t="n">
-        <v>7047233</v>
+        <v>7047126</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
